--- a/dim_accounts.xlsx
+++ b/dim_accounts.xlsx
@@ -1,24 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HAH_Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8C9774-BDB5-4646-9FA3-568522026C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5437F663-C433-41BF-89F7-FF1818234147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{8A284173-2657-664C-9AB5-CF007D435F7B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{8A284173-2657-664C-9AB5-CF007D435F7B}"/>
   </bookViews>
   <sheets>
-    <sheet name="dim_pnl_relations" sheetId="5" r:id="rId1"/>
+    <sheet name="dimacc_pnl_relations" sheetId="5" r:id="rId1"/>
     <sheet name="dim_account" sheetId="1" r:id="rId2"/>
-    <sheet name="dim_account_relation" sheetId="2" r:id="rId3"/>
+    <sheet name="dimacc_bs_relation" sheetId="2" r:id="rId3"/>
     <sheet name="dim_account_reportingline" sheetId="7" r:id="rId4"/>
     <sheet name="account_relationship" sheetId="3" r:id="rId5"/>
-    <sheet name="measure_display" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -93,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="316">
   <si>
     <t>sign</t>
   </si>
@@ -945,30 +944,6 @@
   </si>
   <si>
     <t>158</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>KNTT ngắn hạn</t>
-  </si>
-  <si>
-    <t>KNTT</t>
-  </si>
-  <si>
-    <t>KNTT nhanh</t>
-  </si>
-  <si>
-    <t>KNTT tức thời</t>
-  </si>
-  <si>
-    <t>KNTT lãi vay</t>
   </si>
   <si>
     <t>Font</t>
@@ -1892,18 +1867,6 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{97ADA5F3-16CC-B843-916C-D3B4E09DBD60}" name="Table5" displayName="Table5" ref="A1:C5" totalsRowShown="0">
-  <autoFilter ref="A1:C5" xr:uid="{97ADA5F3-16CC-B843-916C-D3B4E09DBD60}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B312CC02-C9ED-C544-8374-425BC6CA185A}" name="id"/>
-    <tableColumn id="2" xr3:uid="{8DC0AA77-516B-5E40-9BFA-DE876398B515}" name="name"/>
-    <tableColumn id="3" xr3:uid="{0E907955-221D-F049-BA53-F34C792CCFFA}" name="group"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2246,13 +2209,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -2263,7 +2226,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>7</v>
@@ -2290,7 +2253,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>7</v>
@@ -2317,7 +2280,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>7</v>
@@ -2344,7 +2307,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>21</v>
@@ -2371,7 +2334,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>7</v>
@@ -2398,7 +2361,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>7</v>
@@ -2425,7 +2388,7 @@
         <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>21</v>
@@ -2476,7 +2439,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>7</v>
@@ -2503,7 +2466,7 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>21</v>
@@ -2527,10 +2490,10 @@
         <v>-1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>21</v>
@@ -2557,7 +2520,7 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>7</v>
@@ -2584,7 +2547,7 @@
         <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>7</v>
@@ -2611,7 +2574,7 @@
         <v>32</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>21</v>
@@ -2638,7 +2601,7 @@
         <v>34</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>7</v>
@@ -2665,7 +2628,7 @@
         <v>36</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>7</v>
@@ -2692,7 +2655,7 @@
         <v>38</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>21</v>
@@ -2719,7 +2682,7 @@
         <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>21</v>
@@ -2746,7 +2709,7 @@
         <v>42</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>7</v>
@@ -2767,10 +2730,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B21" s="2" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>7</v>
@@ -2794,7 +2757,7 @@
         <v>62</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>7</v>
@@ -7952,10 +7915,10 @@
         <v>1</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>232</v>
@@ -7976,7 +7939,7 @@
         <v>243</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="K83" s="5" t="s">
         <v>241</v>
@@ -8095,16 +8058,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -8122,7 +8085,7 @@
         <v>Tổng cộng tài sản</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="F2" s="4">
         <v>1</v>
@@ -8146,7 +8109,7 @@
         <v xml:space="preserve">  Tài sản ngắn hạn</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="F3" s="4">
         <v>2</v>
@@ -8170,7 +8133,7 @@
         <v xml:space="preserve">    Tiền</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F4" s="8">
         <v>3</v>
@@ -8194,7 +8157,7 @@
         <v xml:space="preserve">    Các khoản tương đương tiền</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F5" s="8">
         <v>3</v>
@@ -8218,7 +8181,7 @@
         <v xml:space="preserve">    Chứng khoán kinh doanh</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F6" s="8">
         <v>3</v>
@@ -8242,7 +8205,7 @@
         <v xml:space="preserve">    Dự phòng giảm giá chứng khoán kinh doanh</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F7" s="8">
         <v>3</v>
@@ -8266,7 +8229,7 @@
         <v xml:space="preserve">    Đầu tư nắm giữ đến ngày đáo hạn (123)</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F8" s="8">
         <v>3</v>
@@ -8290,7 +8253,7 @@
         <v xml:space="preserve">    Phải thu ngắn hạn của khách hàng</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F9" s="8">
         <v>3</v>
@@ -8314,7 +8277,7 @@
         <v xml:space="preserve">    Trả trước cho người bán ngắn hạn</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F10" s="8">
         <v>3</v>
@@ -8338,7 +8301,7 @@
         <v xml:space="preserve">    Phải thu nội bộ ngắn hạn</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F11" s="8">
         <v>3</v>
@@ -8362,7 +8325,7 @@
         <v xml:space="preserve">    Phải thu theo tiến độ kế hoạch hợp đồng xây dựng</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F12" s="8">
         <v>3</v>
@@ -8386,7 +8349,7 @@
         <v xml:space="preserve">    Phải thu về cho vay ngắn hạn</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F13" s="8">
         <v>3</v>
@@ -8410,7 +8373,7 @@
         <v xml:space="preserve">    Các khoản phải thu ngắn hạn khác</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F14" s="8">
         <v>3</v>
@@ -8434,7 +8397,7 @@
         <v xml:space="preserve">    Dự phòng phải thu ngắn hạn khó đòi</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F15" s="8">
         <v>3</v>
@@ -8458,7 +8421,7 @@
         <v xml:space="preserve">    Tài sản thiếu chờ xử lý</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F16" s="8">
         <v>3</v>
@@ -8482,7 +8445,7 @@
         <v xml:space="preserve">    Hàng tồn kho (141)</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F17" s="8">
         <v>3</v>
@@ -8506,7 +8469,7 @@
         <v xml:space="preserve">    Dự phòng giảm giá hàng tồn kho</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F18" s="8">
         <v>3</v>
@@ -8530,7 +8493,7 @@
         <v xml:space="preserve">    Chi phí trả trước ngắn hạn</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F19" s="8">
         <v>3</v>
@@ -8554,7 +8517,7 @@
         <v xml:space="preserve">    Thuế GTGT được khấu trừ</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F20" s="8">
         <v>3</v>
@@ -8578,7 +8541,7 @@
         <v xml:space="preserve">    Thuế và các khoản khác phải thu nhà nước</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F21" s="8">
         <v>3</v>
@@ -8602,7 +8565,7 @@
         <v xml:space="preserve">    Giao dịch mua bán lại trái phiếu Chính phủ (154)</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F22" s="8">
         <v>3</v>
@@ -8626,7 +8589,7 @@
         <v xml:space="preserve">    Tài sản ngắn hạn khác</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F23" s="8">
         <v>3</v>
@@ -8650,7 +8613,7 @@
         <v xml:space="preserve">  Tài sản dài hạn</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="F24" s="4">
         <v>2</v>
@@ -8674,7 +8637,7 @@
         <v xml:space="preserve">    Phải thu dài hạn của khách hàng</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F25" s="8">
         <v>3</v>
@@ -8698,7 +8661,7 @@
         <v xml:space="preserve">    Trả trước cho người bán dài hạn</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F26" s="8">
         <v>3</v>
@@ -8722,7 +8685,7 @@
         <v xml:space="preserve">    Vốn kinh doanh ở đơn vị trực thuộc</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F27" s="8">
         <v>3</v>
@@ -8746,7 +8709,7 @@
         <v xml:space="preserve">    Phải thu dài hạn nội bộ</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F28" s="8">
         <v>3</v>
@@ -8770,7 +8733,7 @@
         <v xml:space="preserve">    Phải thu về cho vay dài hạn</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F29" s="8">
         <v>3</v>
@@ -8794,7 +8757,7 @@
         <v xml:space="preserve">    Phải thu dài hạn khác</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F30" s="8">
         <v>3</v>
@@ -8818,7 +8781,7 @@
         <v xml:space="preserve">    Dự phòng phải thu dài hạn khó đòi</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F31" s="8">
         <v>3</v>
@@ -8842,7 +8805,7 @@
         <v xml:space="preserve">    Tài sản cố định hữu hình</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F32" s="8">
         <v>3</v>
@@ -8866,7 +8829,7 @@
         <v xml:space="preserve">    Tài sản cố định thuê tài chính</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F33" s="8">
         <v>3</v>
@@ -8890,7 +8853,7 @@
         <v xml:space="preserve">    Tài sản cố định vô hình</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F34" s="8">
         <v>3</v>
@@ -8914,7 +8877,7 @@
         <v xml:space="preserve">    Bất động sản đầu tư</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F35" s="8">
         <v>3</v>
@@ -8938,7 +8901,7 @@
         <v xml:space="preserve">    Chi phí sản xuất, kinh doanh dở dang dài hạn</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F36" s="8">
         <v>3</v>
@@ -8962,7 +8925,7 @@
         <v xml:space="preserve">    Chi phí xây dựng cơ bản dở dang</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F37" s="8">
         <v>3</v>
@@ -8986,7 +8949,7 @@
         <v xml:space="preserve">    Đầu tư vào công ty con</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F38" s="8">
         <v>3</v>
@@ -9010,7 +8973,7 @@
         <v xml:space="preserve">    Đầu tư vào công ty liên kết, liên doanh</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F39" s="8">
         <v>3</v>
@@ -9034,7 +8997,7 @@
         <v xml:space="preserve">    Đầu tư góp vốn vào đơn vị khác</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F40" s="8">
         <v>3</v>
@@ -9058,7 +9021,7 @@
         <v xml:space="preserve">    Dự phòng giảm giá đầu tư tài chính dài hạn</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F41" s="8">
         <v>3</v>
@@ -9082,7 +9045,7 @@
         <v xml:space="preserve">    Đầu tư nắm giữ đến ngày đáo hạn (255)</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F42" s="8">
         <v>3</v>
@@ -9106,7 +9069,7 @@
         <v xml:space="preserve">    Chi phí trả trước dài hạn</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F43" s="8">
         <v>3</v>
@@ -9130,7 +9093,7 @@
         <v xml:space="preserve">    Tài sản thuế thu nhập hoãn lại</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F44" s="8">
         <v>3</v>
@@ -9154,7 +9117,7 @@
         <v xml:space="preserve">    Thiết bị, vật tư, phụ tùng thay thế dài hạn</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F45" s="8">
         <v>3</v>
@@ -9178,7 +9141,7 @@
         <v xml:space="preserve">    Tài sản dài hạn khác (268)</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F46" s="8">
         <v>3</v>
@@ -9202,7 +9165,7 @@
         <v>Tổng cộng nguồn vốn</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="F47" s="4">
         <v>1</v>
@@ -9226,7 +9189,7 @@
         <v xml:space="preserve">  Nợ phải trả</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="F48" s="4">
         <v>2</v>
@@ -9250,7 +9213,7 @@
         <v xml:space="preserve">    Phải trả người bán ngắn hạn</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F49" s="8">
         <v>3</v>
@@ -9274,7 +9237,7 @@
         <v xml:space="preserve">    Người mua trả tiền trước ngắn hạn</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F50" s="8">
         <v>3</v>
@@ -9298,7 +9261,7 @@
         <v xml:space="preserve">    Thuế và các khoản phải nộp Nhà nước</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F51" s="8">
         <v>3</v>
@@ -9322,7 +9285,7 @@
         <v xml:space="preserve">    Phải trả người lao động</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F52" s="8">
         <v>3</v>
@@ -9346,7 +9309,7 @@
         <v xml:space="preserve">    Chi phí phải trả ngắn hạn</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F53" s="8">
         <v>3</v>
@@ -9370,7 +9333,7 @@
         <v xml:space="preserve">    Phải trả nội bộ ngắn hạn</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F54" s="8">
         <v>3</v>
@@ -9394,7 +9357,7 @@
         <v xml:space="preserve">    Phải trả theo tiến độ kế hoạch hợp đồng xây dựng</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F55" s="8">
         <v>3</v>
@@ -9418,7 +9381,7 @@
         <v xml:space="preserve">    Doanh thu chưa thực hiện ngắn hạn</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F56" s="8">
         <v>3</v>
@@ -9442,7 +9405,7 @@
         <v xml:space="preserve">    Phải trả ngắn hạn khác</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F57" s="8">
         <v>3</v>
@@ -9466,7 +9429,7 @@
         <v xml:space="preserve">    Vay và nợ thuê tài chính ngắn hạn</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F58" s="8">
         <v>3</v>
@@ -9490,7 +9453,7 @@
         <v xml:space="preserve">    Dự phòng phải trả ngắn hạn</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F59" s="8">
         <v>3</v>
@@ -9514,7 +9477,7 @@
         <v xml:space="preserve">    Quỹ khen thưởng phúc lợi</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F60" s="8">
         <v>3</v>
@@ -9538,7 +9501,7 @@
         <v xml:space="preserve">    Quỹ bình ổn giá</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F61" s="8">
         <v>3</v>
@@ -9562,7 +9525,7 @@
         <v xml:space="preserve">    Giao dịch mua bán lại trái phiếu Chính phủ (324)</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F62" s="8">
         <v>3</v>
@@ -9586,7 +9549,7 @@
         <v xml:space="preserve">    Phải trả người bán dài hạn</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F63" s="8">
         <v>3</v>
@@ -9610,7 +9573,7 @@
         <v xml:space="preserve">    Người mua trả tiền trước dài hạn</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F64" s="8">
         <v>3</v>
@@ -9634,7 +9597,7 @@
         <v xml:space="preserve">    Chi phí trả dài hạn</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F65" s="8">
         <v>3</v>
@@ -9658,7 +9621,7 @@
         <v xml:space="preserve">    Phải trả nội bộ về vốn kinh doanh</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F66" s="8">
         <v>3</v>
@@ -9682,7 +9645,7 @@
         <v xml:space="preserve">    Phải trả dài hạn nội bộ</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F67" s="8">
         <v>3</v>
@@ -9706,7 +9669,7 @@
         <v xml:space="preserve">    Doanh thu chưa thực hiện dài hạn</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F68" s="8">
         <v>3</v>
@@ -9730,7 +9693,7 @@
         <v xml:space="preserve">    Phải trả dài hạn khác</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F69" s="8">
         <v>3</v>
@@ -9754,7 +9717,7 @@
         <v xml:space="preserve">    Vay và nợ thuê tài chính dài hạn</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F70" s="8">
         <v>3</v>
@@ -9778,7 +9741,7 @@
         <v xml:space="preserve">    Trái phiếu chuyển đổi</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F71" s="8">
         <v>3</v>
@@ -9802,7 +9765,7 @@
         <v xml:space="preserve">    Cổ phiếu ưu đãi</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F72" s="8">
         <v>3</v>
@@ -9826,7 +9789,7 @@
         <v xml:space="preserve">    Thuế thu nhập hoãn lại phải trả</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F73" s="8">
         <v>3</v>
@@ -9850,7 +9813,7 @@
         <v xml:space="preserve">    Dự phòng phải trả dài hạn</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F74" s="8">
         <v>3</v>
@@ -9874,7 +9837,7 @@
         <v xml:space="preserve">    Quỹ phát triển khoa học và công nghệ</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F75" s="8">
         <v>3</v>
@@ -9898,7 +9861,7 @@
         <v xml:space="preserve">   Vốn chủ sở hữu</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="F76" s="4">
         <v>2</v>
@@ -9922,7 +9885,7 @@
         <v xml:space="preserve">    Vốn đầu tư của chủ sở hữu</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F77" s="8">
         <v>3</v>
@@ -9946,7 +9909,7 @@
         <v xml:space="preserve">    Thặng dư vốn cổ phần</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F78" s="8">
         <v>3</v>
@@ -9970,7 +9933,7 @@
         <v xml:space="preserve">    Quyền chọn chuyển đổi trái phiếu</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F79" s="8">
         <v>3</v>
@@ -9994,7 +9957,7 @@
         <v xml:space="preserve">    Vốn khác của chủ sở hữu</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F80" s="8">
         <v>3</v>
@@ -10018,7 +9981,7 @@
         <v xml:space="preserve">    Cổ phiếu quỹ</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F81" s="8">
         <v>3</v>
@@ -10042,7 +10005,7 @@
         <v xml:space="preserve">    Chênh lệch đánh giá lại tài sản</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F82" s="8">
         <v>3</v>
@@ -10066,7 +10029,7 @@
         <v xml:space="preserve">    Chênh lệch tỷ giá hối đoái</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F83" s="8">
         <v>3</v>
@@ -10090,7 +10053,7 @@
         <v xml:space="preserve">    Quỹ đầu tư phát triển</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F84" s="8">
         <v>3</v>
@@ -10114,7 +10077,7 @@
         <v xml:space="preserve">    Quỹ hỗ trợ sắp xếp doanh nghiệp</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F85" s="8">
         <v>3</v>
@@ -10138,7 +10101,7 @@
         <v xml:space="preserve">    Quỹ khác thuộc vốn chủ sở hữu</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F86" s="8">
         <v>3</v>
@@ -10162,7 +10125,7 @@
         <v xml:space="preserve">    Lợi nhuận sau thuế chưa phân phối</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F87" s="8">
         <v>3</v>
@@ -10186,7 +10149,7 @@
         <v xml:space="preserve">    Nguồn vốn đầu tư XDCB</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F88" s="8">
         <v>3</v>
@@ -10210,7 +10173,7 @@
         <v xml:space="preserve">    Nguồn kinh phí</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F89" s="8">
         <v>3</v>
@@ -10234,7 +10197,7 @@
         <v xml:space="preserve">    Nguồn kinh phí đã hình thành TSCĐ</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F90" s="8">
         <v>3</v>
@@ -10510,81 +10473,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D049CD68-C4DC-0840-A37A-7D9DA2A0DF25}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>290</v>
-      </c>
-      <c r="C4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2fd14304-2b8c-41d0-bfc3-645347cfe32a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ea937b48-90d5-42d9-af5c-10722bf0f9b5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10817,20 +10714,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2fd14304-2b8c-41d0-bfc3-645347cfe32a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ea937b48-90d5-42d9-af5c-10722bf0f9b5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72B552B5-8565-43E3-9E56-6432291BCF24}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{353F7109-5D57-4731-A9A2-41F6D6B1E94D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bebaf4fa-fec9-4dca-a0d4-2b7be2361797"/>
+    <ds:schemaRef ds:uri="2fd14304-2b8c-41d0-bfc3-645347cfe32a"/>
+    <ds:schemaRef ds:uri="ea937b48-90d5-42d9-af5c-10722bf0f9b5"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10855,13 +10754,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{353F7109-5D57-4731-A9A2-41F6D6B1E94D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72B552B5-8565-43E3-9E56-6432291BCF24}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bebaf4fa-fec9-4dca-a0d4-2b7be2361797"/>
-    <ds:schemaRef ds:uri="2fd14304-2b8c-41d0-bfc3-645347cfe32a"/>
-    <ds:schemaRef ds:uri="ea937b48-90d5-42d9-af5c-10722bf0f9b5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>